--- a/data/trans_orig/IP13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94419</t>
+          <t>93856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102291</t>
+          <t>102320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107162</t>
+          <t>106823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116578</t>
+          <t>116619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204505</t>
+          <t>204907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216798</t>
+          <t>216750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236279</t>
+          <t>236096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246219</t>
+          <t>246627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236092</t>
+          <t>235839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246463</t>
+          <t>246925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476532</t>
+          <t>475362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>491172</t>
+          <t>490857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118738</t>
+          <t>119130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>126145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>126573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136363</t>
+          <t>136242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249381</t>
+          <t>249320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260868</t>
+          <t>260693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179593</t>
+          <t>180662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189452</t>
+          <t>189520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194290</t>
+          <t>194932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202811</t>
+          <t>202816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378983</t>
+          <t>378790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390908</t>
+          <t>390992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81258</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641158</t>
+          <t>641694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>657870</t>
+          <t>658371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677748</t>
+          <t>677151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>695220</t>
+          <t>695515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1322463</t>
+          <t>1323554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349325</t>
+          <t>1349661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126863</t>
+          <t>127470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138118</t>
+          <t>138298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124877</t>
+          <t>125420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137204</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257448</t>
+          <t>257475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273201</t>
+          <t>273701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26551</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218105</t>
+          <t>218153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229242</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242440</t>
+          <t>242429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256269</t>
+          <t>256109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464402</t>
+          <t>464721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482274</t>
+          <t>482576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145295</t>
+          <t>145843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154256</t>
+          <t>154237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149156</t>
+          <t>148577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156711</t>
+          <t>156738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>298789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309631</t>
+          <t>309664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156732</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166502</t>
+          <t>166107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161776</t>
+          <t>162119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172518</t>
+          <t>172356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322033</t>
+          <t>322362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336537</t>
+          <t>336402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>101689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>660440</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>681251</t>
+          <t>680325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>692626</t>
+          <t>692099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>714582</t>
+          <t>714387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360050</t>
+          <t>1358926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1389347</t>
+          <t>1388875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116553</t>
+          <t>117240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125817</t>
+          <t>126148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114364</t>
+          <t>114418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121798</t>
+          <t>121860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234625</t>
+          <t>234451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>246377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190013</t>
+          <t>189867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201114</t>
+          <t>201110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239978</t>
+          <t>240993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251431</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434885</t>
+          <t>433911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449384</t>
+          <t>449422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175626</t>
+          <t>175078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185029</t>
+          <t>184980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171719</t>
+          <t>173005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183078</t>
+          <t>183276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351810</t>
+          <t>351473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365991</t>
+          <t>365640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161604</t>
+          <t>162391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170793</t>
+          <t>170863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160673</t>
+          <t>162122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171006</t>
+          <t>171008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327067</t>
+          <t>327890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340265</t>
+          <t>340426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>657200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>675904</t>
+          <t>675810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700837</t>
+          <t>701725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720231</t>
+          <t>720800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365671</t>
+          <t>1365595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1392094</t>
+          <t>1391600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49896</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106831</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115026</t>
+          <t>114885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>144235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153937</t>
+          <t>154186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159861</t>
+          <t>160855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172475</t>
+          <t>172690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309243</t>
+          <t>309794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324713</t>
+          <t>324302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156226</t>
+          <t>155882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167097</t>
+          <t>167028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189055</t>
+          <t>188319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202844</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348167</t>
+          <t>348492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367115</t>
+          <t>367366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>39900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253835</t>
+          <t>253885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267398</t>
+          <t>267139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281505</t>
+          <t>283117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296539</t>
+          <t>297003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541332</t>
+          <t>541040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>560799</t>
+          <t>560362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>617047</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637527</t>
+          <t>637340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1324469</t>
+          <t>1324144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1355278</t>
+          <t>1355038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13922</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7398</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3851</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12315</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12099</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14557</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>22882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112768</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>107458</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116350</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98773</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93856</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>102320</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>94072</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>102418</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112768</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>106823</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116619</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204907</t>
+          <t>204669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216750</t>
+          <t>216908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>11814</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7300</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18296</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>11186</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17109</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6843</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17325</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11814</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17917</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241942</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>235460</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>246456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>242019</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>236096</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>246627</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>235880</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>246362</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>241942</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>235839</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>246925</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>475362</t>
+          <t>475829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>490857</t>
+          <t>490110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5410</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15284</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3737</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8418</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8088</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9191</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5273</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14942</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132324</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126231</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>136105</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>123811</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119130</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126145</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>119460</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126195</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>132324</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126573</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>136242</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249320</t>
+          <t>248976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260693</t>
+          <t>260797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6513</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12441</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8089</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13435</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13798</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3233</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11117</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199536</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>193608</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202695</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>186008</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>180662</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189520</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>180299</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189582</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199536</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>194932</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202816</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378790</t>
+          <t>378949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390992</t>
+          <t>390398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27358</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46481</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>39327</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21917</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39561</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27185</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>45549</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54060</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>686570</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676219</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>695342</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>650611</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>641694</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>658371</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>641460</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>659104</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>686570</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>677151</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>695515</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1323554</t>
+          <t>1324821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349661</t>
+          <t>1349824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11744</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6714</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18161</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12427</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7881</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7921</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19422</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11744</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7005</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18496</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>132172</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>125755</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>137202</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133752</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127470</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>138298</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>126757</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>138258</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>132172</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>125420</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136911</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257475</t>
+          <t>257349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273701</t>
+          <t>273169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>143916</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>143916</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>143916</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146179</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146179</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146179</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>143916</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>143916</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>143916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18879</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12403</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26798</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11051</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17470</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6381</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18879</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12882</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26562</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>38673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250112</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>242193</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256588</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>224572</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>218153</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>229307</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>217895</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>229242</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250112</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>242429</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256109</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464721</t>
+          <t>465942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482576</t>
+          <t>483235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235623</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235623</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9312</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6161</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11200</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11138</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9994</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154168</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149259</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157230</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>150882</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145843</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154237</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145905</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153752</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154168</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148577</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156738</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298789</t>
+          <t>298261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309664</t>
+          <t>309219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11074</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17734</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8983</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14356</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11074</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6599</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16836</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161221</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>172318</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162354</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156981</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166107</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156169</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166542</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167881</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162119</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>172356</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322362</t>
+          <t>321440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336402</t>
+          <t>336633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,107 +4042,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36103</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29857</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50555</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29760</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36046</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58334</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>84722</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>70068</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>100074</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>84722</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>71740</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>101689</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4155,107 +4155,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>704333</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>692709</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>714330</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>968</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>671561</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>659627</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680325</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>659487</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680422</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>704333</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>692099</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>714387</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1375893</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1360541</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1390547</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>95,2%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1375893</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1358926</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1388875</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2272</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9719</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9565</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5506</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5651</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15583</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9746</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119176</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114445</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121892</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>122089</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>117240</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>126148</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>116071</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>126003</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>119176</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114418</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121860</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234451</t>
+          <t>233879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246377</t>
+          <t>246133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14336</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9407</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20650</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9705</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20706</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11425</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6331</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17068</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>246636</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>240382</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>251009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>196181</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>189867</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>201110</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>189811</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>200812</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>246636</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>240993</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>251730</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433911</t>
+          <t>433853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449422</t>
+          <t>448935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9688</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5382</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16710</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7556</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13821</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3958</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13217</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9688</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5296</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15567</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>178884</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>171862</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>183190</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>181343</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>175078</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184980</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>175682</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>184941</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>178884</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>173005</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>183276</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351473</t>
+          <t>351272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365640</t>
+          <t>365967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6785</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12513</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5609</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2438</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10910</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10667</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6785</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11926</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167263</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161535</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170632</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167692</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162391</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170863</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>162634</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170946</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167263</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162122</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171008</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327890</t>
+          <t>327510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340426</t>
+          <t>339955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43080</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28561</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47171</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28392</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46841</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24044</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43119</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>86489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>711958</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>701764</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720503</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>667306</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>657200</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>675810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>657530</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>675979</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>711958</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>701725</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720800</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365595</t>
+          <t>1362726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391600</t>
+          <t>1390598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7420</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49505</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53542</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50091</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55886</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58189</t>
+          <t>48596</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>96253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>91832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114885</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11962</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17835</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9081</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15064</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>145023</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>139150</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>149221</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>150218</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144235</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154186</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>167360</t>
+          <t>137208</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160855</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172690</t>
+          <t>140912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>317579</t>
+          <t>282230</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309794</t>
+          <t>274843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324302</t>
+          <t>287744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15784</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9685</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23277</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10549</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17190</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>184342</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>176849</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>190441</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>162523</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155882</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>167028</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>164130</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188319</t>
+          <t>156941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202628</t>
+          <t>168357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>359326</t>
+          <t>348472</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348492</t>
+          <t>338223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367366</t>
+          <t>356305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15007</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8751</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23520</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13839</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8319</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21573</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>277638</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>269125</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>283894</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>261619</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>253885</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>267139</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>290479</t>
+          <t>242123</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283117</t>
+          <t>234147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297003</t>
+          <t>247328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>552098</t>
+          <t>519762</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541040</t>
+          <t>509666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>560362</t>
+          <t>528096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35761</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58317</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47236</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71550</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102444</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>627903</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>618104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>637340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>592056</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>581075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1340734</t>
+          <t>1246716</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1324144</t>
+          <t>1229241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1355038</t>
+          <t>1260932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
